--- a/Tailieu/Nganhangdaimport/sao_ke_T8.xlsx
+++ b/Tailieu/Nganhangdaimport/sao_ke_T8.xlsx
@@ -53,51 +53,54 @@
     <t>8/11</t>
   </si>
   <si>
+    <t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN NAM VIET-030826-10:27:09 6215ASCB02TBK9RH</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Bùi Ngọc Thâu</t>
+  </si>
+  <si>
+    <t>THAU</t>
+  </si>
+  <si>
+    <t>8/12</t>
+  </si>
+  <si>
+    <t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN MUA MAY CHAM CONG CUA CTY CHIEM BON</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH BÁCH NIÊN THIÊN ĐỨC VŨNG TÀU</t>
+  </si>
+  <si>
+    <t>6633</t>
+  </si>
+  <si>
+    <t>8/13</t>
+  </si>
+  <si>
+    <t>Nap vao tai khoan cty FT26215650130767 GD 6215IBT1kCTBWQNA 030826-14:53:57</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>8/14</t>
+  </si>
+  <si>
     <t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN DAI TAI LOC-030826-14:55:25 6215ASCB02T1F86M</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>11211</t>
-  </si>
-  <si>
     <t>CÔNG TY CỔ PHẦN ĐẦU TƯ ĐIỆN MÁY XANH</t>
   </si>
   <si>
     <t>7354</t>
   </si>
   <si>
-    <t>8/12</t>
-  </si>
-  <si>
-    <t>Nap vao tai khoan cty FT26215650130767 GD 6215IBT1kCTBWQNA 030826-14:53:57</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>8/13</t>
-  </si>
-  <si>
-    <t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN MUA MAY CHAM CONG CUA CTY CHIEM BON</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>CÔNG TY TNHH BÁCH NIÊN THIÊN ĐỨC VŨNG TÀU</t>
-  </si>
-  <si>
-    <t>6633</t>
-  </si>
-  <si>
-    <t>8/14</t>
-  </si>
-  <si>
-    <t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN NAM VIET-030826-10:27:09 6215ASCB02TBK9RH</t>
-  </si>
-  <si>
     <t>8/10</t>
   </si>
   <si>
@@ -110,45 +113,45 @@
     <t>8/5</t>
   </si>
   <si>
+    <t>My Nam TT phan mem GD 6219MCOBQ21JS6VS 070826-10:17:50</t>
+  </si>
+  <si>
+    <t>TT Phân Tích và Đo Đạc MT Phương Nam</t>
+  </si>
+  <si>
+    <t>22119</t>
+  </si>
+  <si>
+    <t>8/6</t>
+  </si>
+  <si>
+    <t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN NANG CAP SUA CHUA MAY TINH CHO CTY CHIEM BON THEO HD SO 46 NGAY 6.8.2026</t>
+  </si>
+  <si>
+    <t>8/7</t>
+  </si>
+  <si>
+    <t>(SoThe:422926******3289)NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO tracenbr:825248 as 2026-08-07:114438</t>
+  </si>
+  <si>
+    <t>8/8</t>
+  </si>
+  <si>
+    <t>CTY TNHH MY THUAT SX DV THUONG MAI PHUONG LONG-THEO HD SO 45 KY NGAY 5/8/2026</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH MỸ THUẬT - SẢN XUẤT - DỊCH VỤ - THƯƠNG MẠI PHƯỢNG LONG</t>
+  </si>
+  <si>
+    <t>1263</t>
+  </si>
+  <si>
+    <t>8/9</t>
+  </si>
+  <si>
     <t>(SoThe:422926******3289)NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO tracenbr:887835 as 2026-08-07:040130</t>
   </si>
   <si>
-    <t>8/6</t>
-  </si>
-  <si>
-    <t>CTY TNHH MY THUAT SX DV THUONG MAI PHUONG LONG-THEO HD SO 45 KY NGAY 5/8/2026</t>
-  </si>
-  <si>
-    <t>CÔNG TY TNHH MỸ THUẬT - SẢN XUẤT - DỊCH VỤ - THƯƠNG MẠI PHƯỢNG LONG</t>
-  </si>
-  <si>
-    <t>1263</t>
-  </si>
-  <si>
-    <t>8/7</t>
-  </si>
-  <si>
-    <t>(SoThe:422926******3289)NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO tracenbr:825248 as 2026-08-07:114438</t>
-  </si>
-  <si>
-    <t>8/8</t>
-  </si>
-  <si>
-    <t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN NANG CAP SUA CHUA MAY TINH CHO CTY CHIEM BON THEO HD SO 46 NGAY 6.8.2026</t>
-  </si>
-  <si>
-    <t>8/9</t>
-  </si>
-  <si>
-    <t>My Nam TT phan mem GD 6219MCOBQ21JS6VS 070826-10:17:50</t>
-  </si>
-  <si>
-    <t>TT Phân Tích và Đo Đạc MT Phương Nam</t>
-  </si>
-  <si>
-    <t>22119</t>
-  </si>
-  <si>
     <t>8/4</t>
   </si>
   <si>
@@ -158,16 +161,16 @@
     <t>8/2</t>
   </si>
   <si>
+    <t>Nap vao tai khoan cong ty FT26233576167159 GD 6233IBT1k2QQXLJD 210826-15:59:03</t>
+  </si>
+  <si>
+    <t>8/3</t>
+  </si>
+  <si>
     <t>CTY CHIEM BON THANH TOAN HD 3442-210826-16:01:27 6233ASCB02RYB1JG</t>
   </si>
   <si>
     <t>3442</t>
-  </si>
-  <si>
-    <t>8/3</t>
-  </si>
-  <si>
-    <t>Nap vao tai khoan cong ty FT26233576167159 GD 6233IBT1k2QQXLJD 210826-15:59:03</t>
   </si>
   <si>
     <t>8/1</t>
@@ -614,7 +617,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="4">
-        <v>3900000</v>
+        <v>331</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -649,16 +652,22 @@
         <v>19</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F3" s="4">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G3" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c t="s" r="H3" s="6">
+        <v>15</v>
+      </c>
+      <c t="s" r="I3" s="3">
         <v>20</v>
+      </c>
+      <c t="s" r="J3" s="7">
+        <v>21</v>
       </c>
       <c t="b" r="L3" s="3">
         <v>1</v>
@@ -672,28 +681,22 @@
         <v>46237</v>
       </c>
       <c t="s" r="C4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c t="s" r="D4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F4" s="4">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G4" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c t="s" r="H4" s="6">
-        <v>23</v>
-      </c>
-      <c t="s" r="I4" s="3">
-        <v>24</v>
-      </c>
-      <c t="s" r="J4" s="7">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c t="b" r="L4" s="3">
         <v>1</v>
@@ -707,13 +710,13 @@
         <v>46237</v>
       </c>
       <c t="s" r="C5" s="3">
+        <v>25</v>
+      </c>
+      <c t="s" r="D5" s="3">
         <v>26</v>
       </c>
-      <c t="s" r="D5" s="3">
-        <v>27</v>
-      </c>
       <c r="E5" s="4">
-        <v>1500000</v>
+        <v>331</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -725,10 +728,10 @@
         <v>15</v>
       </c>
       <c t="s" r="I5" s="3">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="J5" s="7">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c t="b" r="L5" s="3">
         <v>1</v>
@@ -742,25 +745,25 @@
         <v>46238</v>
       </c>
       <c t="s" r="C6" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="D6" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F6" s="4">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G6" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c t="s" r="H6" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c t="s" r="K6" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c t="b" r="L6" s="3">
         <v>1</v>
@@ -774,22 +777,28 @@
         <v>46241</v>
       </c>
       <c t="s" r="C7" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="D7" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="4">
-        <v>2250000</v>
+        <v>11211</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
       <c t="s" r="G7" s="5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c t="s" r="H7" s="6">
         <v>15</v>
+      </c>
+      <c t="s" r="I7" s="3">
+        <v>34</v>
+      </c>
+      <c t="s" r="J7" s="7">
+        <v>35</v>
       </c>
       <c t="b" r="L7" s="3">
         <v>1</v>
@@ -803,28 +812,28 @@
         <v>46241</v>
       </c>
       <c t="s" r="C8" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c t="s" r="D8" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F8" s="4">
-        <v>2260000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G8" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c t="s" r="H8" s="6">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c t="s" r="I8" s="3">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c t="s" r="J8" s="7">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c t="b" r="L8" s="3">
         <v>1</v>
@@ -838,19 +847,19 @@
         <v>46241</v>
       </c>
       <c t="s" r="C9" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="D9" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4">
-        <v>6500000</v>
+        <v>1111</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
       <c t="s" r="G9" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c t="s" r="H9" s="6">
         <v>15</v>
@@ -867,28 +876,28 @@
         <v>46241</v>
       </c>
       <c t="s" r="C10" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c t="s" r="D10" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F10" s="4">
-        <v>5690000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G10" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c t="s" r="H10" s="6">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c t="s" r="I10" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c t="s" r="J10" s="7">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c t="b" r="L10" s="3">
         <v>1</v>
@@ -902,28 +911,22 @@
         <v>46241</v>
       </c>
       <c t="s" r="C11" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="D11" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="F11" s="4">
-        <v>5200000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G11" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c t="s" r="H11" s="6">
-        <v>23</v>
-      </c>
-      <c t="s" r="I11" s="3">
-        <v>43</v>
-      </c>
-      <c t="s" r="J11" s="7">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c t="b" r="L11" s="3">
         <v>1</v>
@@ -937,19 +940,19 @@
         <v>46244</v>
       </c>
       <c t="s" r="C12" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="D12" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="4">
-        <v>7500000</v>
+        <v>1111</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
       <c t="s" r="G12" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c t="s" r="H12" s="6">
         <v>15</v>
@@ -966,25 +969,22 @@
         <v>46255</v>
       </c>
       <c t="s" r="C13" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="D13" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="4">
-        <v>1296000</v>
+        <v>11211</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
       <c t="s" r="G13" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c t="s" r="H13" s="6">
         <v>15</v>
-      </c>
-      <c t="s" r="K13" s="3">
-        <v>49</v>
       </c>
       <c t="b" r="L13" s="3">
         <v>1</v>
@@ -1004,16 +1004,19 @@
         <v>51</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="F14" s="4">
-        <v>1512000</v>
+        <v>0</v>
       </c>
       <c t="s" r="G14" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c t="s" r="H14" s="6">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c t="s" r="K14" s="3">
+        <v>52</v>
       </c>
       <c t="b" r="L14" s="3">
         <v>1</v>
@@ -1027,22 +1030,22 @@
         <v>46259</v>
       </c>
       <c t="s" r="C15" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="D15" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>11211</v>
       </c>
       <c r="F15" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c t="s" r="G15" s="5">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c t="s" r="H15" s="6">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c t="b" r="L15" s="3">
         <v>1</v>
